--- a/product_selector_out/STM8AF series.xlsx
+++ b/product_selector_out/STM8AF series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG40"/>
+  <dimension ref="A1:AH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.3671875" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,8 @@
     <col width="18" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -716,6 +717,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -883,6 +889,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1050,6 +1061,11 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1217,6 +1233,11 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1384,6 +1405,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1551,6 +1577,11 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1718,6 +1749,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1885,6 +1921,11 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -2052,6 +2093,11 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -2219,6 +2265,11 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2386,6 +2437,11 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2553,6 +2609,11 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2720,6 +2781,11 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2887,6 +2953,11 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -3054,6 +3125,11 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3221,6 +3297,11 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3388,6 +3469,11 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3555,6 +3641,11 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3722,6 +3813,11 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -3889,6 +3985,11 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -4056,6 +4157,11 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -4223,6 +4329,11 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -4390,6 +4501,11 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -4557,6 +4673,11 @@
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -4724,6 +4845,11 @@
       </c>
       <c r="AG34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -4891,6 +5017,11 @@
       </c>
       <c r="AG35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6366.pdf</t>
         </is>
       </c>
@@ -5058,6 +5189,11 @@
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6388.pdf</t>
         </is>
       </c>
@@ -5225,6 +5361,11 @@
       </c>
       <c r="AG37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -5392,6 +5533,11 @@
       </c>
       <c r="AG38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -5559,6 +5705,11 @@
       </c>
       <c r="AG39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -5726,14 +5877,19 @@
       </c>
       <c r="AG40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -5778,7 +5934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG40"/>
+  <dimension ref="A1:AH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5814,6 +5970,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6000,6 +6157,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -6165,7 +6327,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6332,7 +6499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6499,7 +6671,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6666,7 +6843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6833,7 +7015,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7000,7 +7187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7167,7 +7359,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="6" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7334,7 +7531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="6" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7501,7 +7703,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7668,7 +7875,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="6" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7835,7 +8047,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="6" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8002,7 +8219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="6" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8169,7 +8391,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8336,7 +8563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG24" s="6" t="inlineStr">
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8503,7 +8735,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG25" s="6" t="inlineStr">
+      <c r="AG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8670,7 +8907,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG26" s="6" t="inlineStr">
+      <c r="AG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8837,7 +9079,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG27" s="6" t="inlineStr">
+      <c r="AG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9004,7 +9251,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG28" s="6" t="inlineStr">
+      <c r="AG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9171,7 +9423,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG29" s="6" t="inlineStr">
+      <c r="AG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9338,7 +9595,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
+      <c r="AG30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9505,7 +9767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG31" s="6" t="inlineStr">
+      <c r="AG31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9672,7 +9939,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG32" s="6" t="inlineStr">
+      <c r="AG32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9839,7 +10111,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG33" s="6" t="inlineStr">
+      <c r="AG33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10006,7 +10283,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG34" s="6" t="inlineStr">
+      <c r="AG34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10173,7 +10455,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG35" s="6" t="inlineStr">
+      <c r="AG35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10340,7 +10627,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG36" s="6" t="inlineStr">
+      <c r="AG36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10507,7 +10799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG37" s="6" t="inlineStr">
+      <c r="AG37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10674,7 +10971,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG38" s="6" t="inlineStr">
+      <c r="AG38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10841,7 +11143,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG39" s="6" t="inlineStr">
+      <c r="AG39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11008,7 +11315,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG40" s="6" t="inlineStr">
+      <c r="AG40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11016,8 +11328,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
